--- a/relatorio_imagens_invalidas.xlsx
+++ b/relatorio_imagens_invalidas.xlsx
@@ -14,9 +14,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>arquivo</t>
+  </si>
+  <si>
+    <t>1_DENVERTEC_100_F_18KG.jpg</t>
+  </si>
+  <si>
+    <t>3_DENVERTEC_100_F_18KG.jpg</t>
+  </si>
+  <si>
+    <t>1_EXTENSAO_DANEVA_SORT_2P_+_T_PP_0,75_3MT_.jpg</t>
+  </si>
+  <si>
+    <t>3_PARAFUSO_CHIPBOARD_CHATA_PHILIPS_3125.jpg</t>
+  </si>
+  <si>
+    <t>2_PARAFUSO_CHIPBOARD_CHATA_PHILIPS_3153.jpg</t>
+  </si>
+  <si>
+    <t>3_DENVER_POXI.jpg</t>
+  </si>
+  <si>
+    <t>3_FORMÃO_PACETTA_D_1_2.jpg</t>
+  </si>
+  <si>
+    <t>3_EXTENSÃO_TECHNA_PLACA_0,75_3MT_PRETO.jpg</t>
+  </si>
+  <si>
+    <t>1_EXTENSÃO_TECHNA_PLACA_0,75_3MT_PRETO.jpg</t>
   </si>
 </sst>
 </file>
@@ -374,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +409,51 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
